--- a/artfynd/A 42353-2023 artfynd.xlsx
+++ b/artfynd/A 42353-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42353-2023 artfynd.xlsx
+++ b/artfynd/A 42353-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112687195</v>
+        <v>112685991</v>
       </c>
       <c r="B2" t="n">
-        <v>90412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588771</v>
+        <v>588808</v>
       </c>
       <c r="R2" t="n">
-        <v>6387850</v>
+        <v>6387692</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,51 +784,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112686316</v>
+        <v>112686007</v>
       </c>
       <c r="B3" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588763</v>
+        <v>588835</v>
       </c>
       <c r="R3" t="n">
-        <v>6387835</v>
+        <v>6387740</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,51 +893,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112686302</v>
+        <v>112687195</v>
       </c>
       <c r="B4" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588768</v>
+        <v>588771</v>
       </c>
       <c r="R4" t="n">
-        <v>6387853</v>
+        <v>6387850</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112686479</v>
+        <v>112686030</v>
       </c>
       <c r="B5" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,7 +1032,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1067,14 +1045,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 42353, Glabo, Sm</t>
+          <t>A 42343, Glabo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588748</v>
+        <v>588804</v>
       </c>
       <c r="R5" t="n">
-        <v>6387844</v>
+        <v>6387837</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,15 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112686245</v>
+        <v>112686046</v>
       </c>
       <c r="B6" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,7 +1142,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1186,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588811</v>
+        <v>588807</v>
       </c>
       <c r="R6" t="n">
-        <v>6387826</v>
+        <v>6387834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,15 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112686466</v>
+        <v>112686085</v>
       </c>
       <c r="B7" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1252,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1301,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588757</v>
+        <v>588824</v>
       </c>
       <c r="R7" t="n">
-        <v>6387851</v>
+        <v>6387832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,15 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112686046</v>
+        <v>112686191</v>
       </c>
       <c r="B8" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1362,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1416,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588807</v>
+        <v>588833</v>
       </c>
       <c r="R8" t="n">
-        <v>6387834</v>
+        <v>6387804</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,15 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112686341</v>
+        <v>112686205</v>
       </c>
       <c r="B9" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1472,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588762</v>
+        <v>588826</v>
       </c>
       <c r="R9" t="n">
-        <v>6387851</v>
+        <v>6387812</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,15 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112686512</v>
+        <v>112686245</v>
       </c>
       <c r="B10" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,7 +1582,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1646,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588747</v>
+        <v>588811</v>
       </c>
       <c r="R10" t="n">
-        <v>6387884</v>
+        <v>6387826</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,15 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112686085</v>
+        <v>112686259</v>
       </c>
       <c r="B11" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1692,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1761,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588824</v>
+        <v>588771</v>
       </c>
       <c r="R11" t="n">
-        <v>6387832</v>
+        <v>6387850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,15 +1772,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112686030</v>
+        <v>112686288</v>
       </c>
       <c r="B12" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,11 +1800,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1872,14 +1811,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 42343, Glabo, Sm</t>
+          <t>A 42353, Glabo, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588804</v>
+        <v>588765</v>
       </c>
       <c r="R12" t="n">
-        <v>6387837</v>
+        <v>6387829</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1939,15 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112686288</v>
+        <v>112686302</v>
       </c>
       <c r="B13" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1906,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1987,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588765</v>
+        <v>588768</v>
       </c>
       <c r="R13" t="n">
-        <v>6387829</v>
+        <v>6387853</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2050,50 +1988,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112685991</v>
+        <v>112686316</v>
       </c>
       <c r="B14" t="n">
-        <v>89816</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2101,10 +2035,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588808</v>
+        <v>588763</v>
       </c>
       <c r="R14" t="n">
-        <v>6387692</v>
+        <v>6387835</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2164,15 +2098,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112686205</v>
+        <v>112686341</v>
       </c>
       <c r="B15" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2128,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2216,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588826</v>
+        <v>588762</v>
       </c>
       <c r="R15" t="n">
-        <v>6387812</v>
+        <v>6387851</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,15 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112686191</v>
+        <v>112686466</v>
       </c>
       <c r="B16" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2238,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2331,10 +2255,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588833</v>
+        <v>588757</v>
       </c>
       <c r="R16" t="n">
-        <v>6387804</v>
+        <v>6387851</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2394,50 +2318,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112686007</v>
+        <v>112686479</v>
       </c>
       <c r="B17" t="n">
-        <v>89816</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2445,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588835</v>
+        <v>588748</v>
       </c>
       <c r="R17" t="n">
-        <v>6387740</v>
+        <v>6387844</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2508,15 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112686259</v>
+        <v>112686512</v>
       </c>
       <c r="B18" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,10 +2475,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588771</v>
+        <v>588747</v>
       </c>
       <c r="R18" t="n">
-        <v>6387850</v>
+        <v>6387884</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
